--- a/data/outplant/sequim/outplant_metadata.xlsx
+++ b/data/outplant/sequim/outplant_metadata.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashuffmyer/MyProjects/oysters/polyIC-larvae/data/outplant/sequim/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1199771-7D40-364A-A1E6-60CA3A88C907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF75144D-9C2B-0F4E-B498-1DCCB6B0014E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="12320" windowHeight="17760" xr2:uid="{0DAF8851-3CE0-B641-BA5A-C7AC4208D2FB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="17">
   <si>
     <t>treatment</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>deploy.date</t>
+  </si>
+  <si>
+    <t>added on 9/23/26</t>
   </si>
 </sst>
 </file>
@@ -126,10 +129,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -467,219 +469,219 @@
   <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5" style="1" customWidth="1"/>
-    <col min="3" max="4" width="14.6640625" style="1" customWidth="1"/>
-    <col min="5" max="7" width="10.83203125" style="1"/>
-    <col min="8" max="8" width="16.33203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16" style="1" customWidth="1"/>
-    <col min="10" max="10" width="21" style="1" customWidth="1"/>
-    <col min="11" max="16" width="10.83203125" style="1"/>
-    <col min="17" max="17" width="16.33203125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="18.1640625" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="1" width="16.5" customWidth="1"/>
+    <col min="2" max="2" width="15.5" customWidth="1"/>
+    <col min="3" max="4" width="14.6640625" customWidth="1"/>
+    <col min="8" max="8" width="16.33203125" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="21" customWidth="1"/>
+    <col min="17" max="17" width="16.33203125" customWidth="1"/>
+    <col min="18" max="18" width="18.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
+      <c r="A2">
         <v>33</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2">
         <v>20</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="1">
-        <v>100</v>
-      </c>
-      <c r="F2" s="1">
+      <c r="E2">
+        <v>100</v>
+      </c>
+      <c r="F2">
         <v>22023399</v>
       </c>
-      <c r="G2" s="1">
-        <v>20250710</v>
-      </c>
-      <c r="H2" s="1" t="s">
+      <c r="G2">
+        <v>20250710</v>
+      </c>
+      <c r="H2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
+      <c r="A3">
         <v>34</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3">
         <v>19</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="1">
-        <v>100</v>
-      </c>
-      <c r="F3" s="1">
+      <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3">
         <v>22023398</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3">
         <v>20250710</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
+      <c r="A4">
         <v>49</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4">
         <v>18</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="1">
-        <v>100</v>
-      </c>
-      <c r="G4" s="1">
+      <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="G4">
         <v>20250710</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
+      <c r="A5">
         <v>39</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5">
         <v>17</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="1">
-        <v>100</v>
-      </c>
-      <c r="G5" s="1">
+      <c r="E5">
+        <v>100</v>
+      </c>
+      <c r="G5">
         <v>20250710</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
+      <c r="A6">
         <v>31</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6">
         <v>16</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="1">
-        <v>100</v>
-      </c>
-      <c r="G6" s="1">
+      <c r="E6">
+        <v>100</v>
+      </c>
+      <c r="G6">
         <v>20250710</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
+      <c r="A7">
         <v>60</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7">
         <v>15</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="1">
-        <v>100</v>
-      </c>
-      <c r="G7" s="1">
-        <v>20250710</v>
-      </c>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
+      <c r="E7">
+        <v>100</v>
+      </c>
+      <c r="G7">
+        <v>20250710</v>
+      </c>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
+      <c r="A8">
         <v>40</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8">
         <v>14</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="1">
-        <v>100</v>
-      </c>
-      <c r="G8" s="1">
+      <c r="E8">
+        <v>100</v>
+      </c>
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8">
         <v>20250710</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
+      <c r="A9">
         <v>50</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9">
         <v>13</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="1">
-        <v>100</v>
-      </c>
-      <c r="G9" s="1">
-        <v>20250710</v>
-      </c>
-      <c r="H9" s="1" t="s">
+      <c r="E9">
+        <v>100</v>
+      </c>
+      <c r="G9">
+        <v>20250710</v>
+      </c>
+      <c r="H9" t="s">
         <v>8</v>
       </c>
     </row>
